--- a/04_DESIGN_TABLES/DesignTable_5600.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5600.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1320,24 +1325,59 @@
           <t>5600-20-20-20-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.66</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>5600-20-20-20-FG</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A (1) NPTF) x 1 1/4-11 1/2 (A (2) NPTF) x 1 1/4-11 1/2 (A (3) NPTF)</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'N1 LGTH' = 2.380 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N2@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'N2 LGTH' = 2.380 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N3@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'N3 LGTH' = 2.380 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; Y@HEX: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'Y FLATS' = 1.625 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'A1 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'A2 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-20-20-20-FG column 'A3 DRILL' = 1.250 (catalog_verified.json); OMi Items row 1537: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; THDMAJ_A1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] pipe OD for the part-number dash -20 (OMi Items!U1537 "1 1/4-11 1/2 NPTF", catalog 1-1/4-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] pipe OD for the part-number dash -20 (OMi Items!U1537 "1 1/4-11 1/2 NPTF", catalog 1-1/4-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A3@DRIVE: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] pipe OD for the part-number dash -20 (OMi Items!U1537 "1 1/4-11 1/2 NPTF", catalog 1-1/4-11-1/2); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] thread text, format of the built 5600 rows; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): every body size from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1348,6 +1388,11 @@
       <c r="R15" t="inlineStr">
         <is>
           <t>5600-20-20-20-FG</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1357,24 +1402,59 @@
           <t>5600-24-24-24-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.9</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>5600-24-24-24-FG</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 (A (1) NPTF) x 1 1/2-11 1/2 (A (2) NPTF) x 1 1/2-11 1/2 (A (3) NPTF)</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'N1 LGTH' = 2.640 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N2@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'N2 LGTH' = 2.640 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; N3@DRIVE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'N3 LGTH' = 2.640 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; Y@HEX: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'Y FLATS' = 1.875 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D1@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'A1 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D2@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'A2 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; D3@BORE: Brennan TFA catalog p55 table TFA-p055-t01 (MP-MP-MP TEE (AS CODED PER SAE J846)) row 5600-24-24-24-FG column 'A3 DRILL' = 1.500 (catalog_verified.json); OMi Items row 1538: thread text only, no dimension; no Air-Way row; no own STEP; equals the 2026-10-02 proposal; THDMAJ_A1@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] pipe OD for the part-number dash -24 (OMi Items!U1538 "1 1/2-11 1/2 NPFT", catalog 1-1/2-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A2@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] pipe OD for the part-number dash -24 (OMi Items!U1538 "1 1/2-11 1/2 NPFT", catalog 1-1/2-11-1/2); equals the 2026-10-02 proposal; THDMAJ_A3@DRIVE: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] pipe OD for the part-number dash -24 (OMi Items!U1538 "1 1/2-11 1/2 NPFT", catalog 1-1/2-11-1/2); equals the 2026-10-02 proposal; $PRP@Threads: ASME B1.20.1 / B1.20.3 1-1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[24] thread text, format of the built 5600 rows; equals the 2026-10-02 proposal</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18): every body size from the Brennan TFA catalog alone</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1385,6 +1465,11 @@
       <c r="R16" t="inlineStr">
         <is>
           <t>5600-24-24-24-FG</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
